--- a/NTu/Mumberes_Potato_results.xlsx
+++ b/NTu/Mumberes_Potato_results.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,32 +417,32 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Year</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>SOC Baseline (t/ha)</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>SOC Project (t/ha)</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>SOC Difference (t/ha)</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Delta SOC (t/ha)</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>ERs (tCO2e/ha)</t>
         </is>
@@ -481,19 +469,19 @@
         <v>2026</v>
       </c>
       <c r="B3" t="n">
-        <v>94.31063845473007</v>
+        <v>98.86090106372485</v>
       </c>
       <c r="C3" t="n">
         <v>113.649862435789</v>
       </c>
       <c r="D3" t="n">
-        <v>19.33922398105896</v>
+        <v>14.78896137206418</v>
       </c>
       <c r="E3" t="n">
-        <v>19.33935824323346</v>
+        <v>14.78909563423868</v>
       </c>
       <c r="F3" t="n">
-        <v>70.91098022518936</v>
+        <v>54.22668399220849</v>
       </c>
     </row>
     <row r="4">
@@ -501,19 +489,19 @@
         <v>2027</v>
       </c>
       <c r="B4" t="n">
-        <v>84.13166288634507</v>
+        <v>91.09336320730948</v>
       </c>
       <c r="C4" t="n">
         <v>113.6498616437091</v>
       </c>
       <c r="D4" t="n">
-        <v>29.51819875736402</v>
+        <v>22.55649843639961</v>
       </c>
       <c r="E4" t="n">
-        <v>10.17897477630505</v>
+        <v>7.767537064335428</v>
       </c>
       <c r="F4" t="n">
-        <v>37.32290751311853</v>
+        <v>28.48096923589657</v>
       </c>
     </row>
     <row r="5">
@@ -521,19 +509,19 @@
         <v>2028</v>
       </c>
       <c r="B5" t="n">
-        <v>77.71351197462079</v>
+        <v>86.22149150960958</v>
       </c>
       <c r="C5" t="n">
         <v>113.6498609222855</v>
       </c>
       <c r="D5" t="n">
-        <v>35.93634894766471</v>
+        <v>27.42836941267592</v>
       </c>
       <c r="E5" t="n">
-        <v>6.418150190300693</v>
+        <v>4.871870976276313</v>
       </c>
       <c r="F5" t="n">
-        <v>23.53321736443587</v>
+        <v>17.86352691301315</v>
       </c>
     </row>
     <row r="6">
@@ -541,19 +529,19 @@
         <v>2029</v>
       </c>
       <c r="B6" t="n">
-        <v>73.29597316639509</v>
+        <v>82.89972818094112</v>
       </c>
       <c r="C6" t="n">
         <v>113.6498602652155</v>
       </c>
       <c r="D6" t="n">
-        <v>40.35388709882037</v>
+        <v>30.75013208427433</v>
       </c>
       <c r="E6" t="n">
-        <v>4.417538151155654</v>
+        <v>3.321762671598407</v>
       </c>
       <c r="F6" t="n">
-        <v>16.19763988757073</v>
+        <v>12.17979646252749</v>
       </c>
     </row>
     <row r="7">
@@ -561,19 +549,19 @@
         <v>2030</v>
       </c>
       <c r="B7" t="n">
-        <v>69.96894673026107</v>
+        <v>80.43111473078217</v>
       </c>
       <c r="C7" t="n">
         <v>113.6498596667584</v>
       </c>
       <c r="D7" t="n">
-        <v>43.68091293649735</v>
+        <v>33.21874493597625</v>
       </c>
       <c r="E7" t="n">
-        <v>3.327025837676985</v>
+        <v>2.46861285170192</v>
       </c>
       <c r="F7" t="n">
-        <v>12.19909473814894</v>
+        <v>9.051580456240373</v>
       </c>
     </row>
     <row r="8">
@@ -581,19 +569,19 @@
         <v>2031</v>
       </c>
       <c r="B8" t="n">
-        <v>67.25657224722742</v>
+        <v>78.4501726924627</v>
       </c>
       <c r="C8" t="n">
         <v>113.6498591216859</v>
       </c>
       <c r="D8" t="n">
-        <v>46.39328687445847</v>
+        <v>35.19968642922319</v>
       </c>
       <c r="E8" t="n">
-        <v>2.712373937961118</v>
+        <v>1.980941493246945</v>
       </c>
       <c r="F8" t="n">
-        <v>9.945371105857433</v>
+        <v>7.263452141905465</v>
       </c>
     </row>
     <row r="9">
@@ -601,19 +589,19 @@
         <v>2032</v>
       </c>
       <c r="B9" t="n">
-        <v>64.90783478567516</v>
+        <v>76.76321827509855</v>
       </c>
       <c r="C9" t="n">
         <v>113.6498586252358</v>
       </c>
       <c r="D9" t="n">
-        <v>48.74202383956064</v>
+        <v>36.88664035013726</v>
       </c>
       <c r="E9" t="n">
-        <v>2.348736965102177</v>
+        <v>1.686953920914064</v>
       </c>
       <c r="F9" t="n">
-        <v>8.61203553870798</v>
+        <v>6.185497710018235</v>
       </c>
     </row>
     <row r="10">
@@ -621,19 +609,19 @@
         <v>2033</v>
       </c>
       <c r="B10" t="n">
-        <v>62.78909221902841</v>
+        <v>75.26636651718594</v>
       </c>
       <c r="C10" t="n">
         <v>113.6498581730708</v>
       </c>
       <c r="D10" t="n">
-        <v>50.86076595404241</v>
+        <v>38.38349165588488</v>
       </c>
       <c r="E10" t="n">
-        <v>2.118742114481769</v>
+        <v>1.496851305747626</v>
       </c>
       <c r="F10" t="n">
-        <v>7.768721086433153</v>
+        <v>5.488454787741294</v>
       </c>
     </row>
     <row r="11">
@@ -641,19 +629,19 @@
         <v>2034</v>
       </c>
       <c r="B11" t="n">
-        <v>60.82828806518514</v>
+        <v>73.9029394989028</v>
       </c>
       <c r="C11" t="n">
         <v>113.6498577612406</v>
       </c>
       <c r="D11" t="n">
-        <v>52.82156969605546</v>
+        <v>39.7469182623378</v>
       </c>
       <c r="E11" t="n">
-        <v>1.960803742013042</v>
+        <v>1.363426606452919</v>
       </c>
       <c r="F11" t="n">
-        <v>7.189613720714486</v>
+        <v>4.999230890327368</v>
       </c>
     </row>
     <row r="12">
@@ -661,19 +649,19 @@
         <v>2035</v>
       </c>
       <c r="B12" t="n">
-        <v>58.98580328820606</v>
+        <v>72.64119295045948</v>
       </c>
       <c r="C12" t="n">
         <v>113.6498573861471</v>
       </c>
       <c r="D12" t="n">
-        <v>54.66405409794105</v>
+        <v>41.00866443568763</v>
       </c>
       <c r="E12" t="n">
-        <v>1.842484401885599</v>
+        <v>1.261746173349835</v>
       </c>
       <c r="F12" t="n">
-        <v>6.755776140247197</v>
+        <v>4.62640263561606</v>
       </c>
     </row>
     <row r="13">
@@ -681,19 +669,19 @@
         <v>2036</v>
       </c>
       <c r="B13" t="n">
-        <v>57.23916801140225</v>
+        <v>71.4626211122555</v>
       </c>
       <c r="C13" t="n">
         <v>113.6498570445133</v>
       </c>
       <c r="D13" t="n">
-        <v>56.41068903311102</v>
+        <v>42.18723593225776</v>
       </c>
       <c r="E13" t="n">
-        <v>1.746634935169965</v>
+        <v>1.178571496570129</v>
       </c>
       <c r="F13" t="n">
-        <v>6.404328095623204</v>
+        <v>4.321428820757139</v>
       </c>
     </row>
     <row r="14">
@@ -701,19 +689,19 @@
         <v>2037</v>
       </c>
       <c r="B14" t="n">
-        <v>55.57502345594281</v>
+        <v>70.35579945154568</v>
       </c>
       <c r="C14" t="n">
         <v>113.6498567333544</v>
       </c>
       <c r="D14" t="n">
-        <v>58.07483327741154</v>
+        <v>43.29405728180868</v>
       </c>
       <c r="E14" t="n">
-        <v>1.664144244300523</v>
+        <v>1.106821349550913</v>
       </c>
       <c r="F14" t="n">
-        <v>6.101862229101918</v>
+        <v>4.058344948353347</v>
       </c>
     </row>
     <row r="15">
@@ -721,19 +709,19 @@
         <v>2038</v>
       </c>
       <c r="B15" t="n">
-        <v>53.98488835198817</v>
+        <v>69.31313585406377</v>
       </c>
       <c r="C15" t="n">
         <v>113.649856449952</v>
       </c>
       <c r="D15" t="n">
-        <v>59.66496809796379</v>
+        <v>44.33672059588818</v>
       </c>
       <c r="E15" t="n">
-        <v>1.590134820552244</v>
+        <v>1.042663314079505</v>
       </c>
       <c r="F15" t="n">
-        <v>5.830494342024894</v>
+        <v>3.823098818291518</v>
       </c>
     </row>
     <row r="16">
@@ -741,19 +729,19 @@
         <v>2039</v>
       </c>
       <c r="B16" t="n">
-        <v>52.46292538980569</v>
+        <v>68.32915232199001</v>
       </c>
       <c r="C16" t="n">
         <v>113.64985619183</v>
       </c>
       <c r="D16" t="n">
-        <v>61.18693080202435</v>
+        <v>45.32070386984003</v>
       </c>
       <c r="E16" t="n">
-        <v>1.521962704060563</v>
+        <v>0.9839832739518499</v>
       </c>
       <c r="F16" t="n">
-        <v>5.580529914888731</v>
+        <v>3.607938671156783</v>
       </c>
     </row>
     <row r="17">
@@ -761,19 +749,19 @@
         <v>2040</v>
       </c>
       <c r="B17" t="n">
-        <v>51.00476034761689</v>
+        <v>67.39957311958591</v>
       </c>
       <c r="C17" t="n">
         <v>113.6498559567335</v>
       </c>
       <c r="D17" t="n">
-        <v>62.64509560911658</v>
+        <v>46.25028283714757</v>
       </c>
       <c r="E17" t="n">
-        <v>1.458164807092231</v>
+        <v>0.9295789673075348</v>
       </c>
       <c r="F17" t="n">
-        <v>5.346604292671515</v>
+        <v>3.408456213460961</v>
       </c>
     </row>
     <row r="18">
@@ -781,19 +769,19 @@
         <v>2041</v>
       </c>
       <c r="B18" t="n">
-        <v>49.60685576117017</v>
+        <v>66.52083831293658</v>
       </c>
       <c r="C18" t="n">
         <v>113.6498557426084</v>
       </c>
       <c r="D18" t="n">
-        <v>64.04299998143821</v>
+        <v>47.12901742967182</v>
       </c>
       <c r="E18" t="n">
-        <v>1.397904372321634</v>
+        <v>0.8787345925242533</v>
       </c>
       <c r="F18" t="n">
-        <v>5.125649365179323</v>
+        <v>3.222026839255596</v>
       </c>
     </row>
     <row r="19">
@@ -801,19 +789,19 @@
         <v>2042</v>
       </c>
       <c r="B19" t="n">
-        <v>48.26617696768826</v>
+        <v>65.68984196887516</v>
       </c>
       <c r="C19" t="n">
         <v>113.6498555475841</v>
       </c>
       <c r="D19" t="n">
-        <v>65.38367857989581</v>
+        <v>47.96001357870891</v>
       </c>
       <c r="E19" t="n">
-        <v>1.3406785984576</v>
+        <v>0.830996149037091</v>
       </c>
       <c r="F19" t="n">
-        <v>4.915821527677868</v>
+        <v>3.046985879802667</v>
       </c>
     </row>
     <row r="20">
@@ -821,19 +809,19 @@
         <v>2043</v>
       </c>
       <c r="B20" t="n">
-        <v>46.98001246054192</v>
+        <v>64.90378919495048</v>
       </c>
       <c r="C20" t="n">
         <v>113.6498553699566</v>
       </c>
       <c r="D20" t="n">
-        <v>66.66984290941471</v>
+        <v>48.74606617500615</v>
       </c>
       <c r="E20" t="n">
-        <v>1.286164329518897</v>
+        <v>0.7860525962972389</v>
       </c>
       <c r="F20" t="n">
-        <v>4.715935874902622</v>
+        <v>2.882192853089876</v>
       </c>
     </row>
     <row r="21">
@@ -841,19 +829,19 @@
         <v>2044</v>
       </c>
       <c r="B21" t="n">
-        <v>45.74587581155177</v>
+        <v>64.16011620467684</v>
       </c>
       <c r="C21" t="n">
         <v>113.6498552081742</v>
       </c>
       <c r="D21" t="n">
-        <v>67.90397939662246</v>
+        <v>49.48973900349739</v>
       </c>
       <c r="E21" t="n">
-        <v>1.234136487207749</v>
+        <v>0.7436728284912419</v>
       </c>
       <c r="F21" t="n">
-        <v>4.525167119761747</v>
+        <v>2.726800371134554</v>
       </c>
     </row>
     <row r="22">
@@ -861,19 +849,19 @@
         <v>2045</v>
       </c>
       <c r="B22" t="n">
-        <v>44.5614508156868</v>
+        <v>63.45644394759989</v>
       </c>
       <c r="C22" t="n">
         <v>113.6498550608233</v>
       </c>
       <c r="D22" t="n">
-        <v>69.08840424513653</v>
+        <v>50.19341111322343</v>
       </c>
       <c r="E22" t="n">
-        <v>1.18442484851407</v>
+        <v>0.7036721097260425</v>
       </c>
       <c r="F22" t="n">
-        <v>4.342891111218255</v>
+        <v>2.580131068995489</v>
       </c>
     </row>
     <row r="23">
@@ -881,19 +869,19 @@
         <v>2046</v>
       </c>
       <c r="B23" t="n">
-        <v>43.4245596334225</v>
+        <v>62.79054974065253</v>
       </c>
       <c r="C23" t="n">
         <v>113.6498549266166</v>
       </c>
       <c r="D23" t="n">
-        <v>70.22529529319409</v>
+        <v>50.85930518596407</v>
       </c>
       <c r="E23" t="n">
-        <v>1.136891048057564</v>
+        <v>0.6658940727406346</v>
       </c>
       <c r="F23" t="n">
-        <v>4.1686005095444</v>
+        <v>2.441611600048994</v>
       </c>
     </row>
     <row r="24">
@@ -901,19 +889,19 @@
         <v>2047</v>
       </c>
       <c r="B24" t="n">
-        <v>42.33314325463682</v>
+        <v>62.16034866770283</v>
       </c>
       <c r="C24" t="n">
         <v>113.6498548043817</v>
       </c>
       <c r="D24" t="n">
-        <v>71.31671154974485</v>
+        <v>51.48950613667885</v>
       </c>
       <c r="E24" t="n">
-        <v>1.091416256550758</v>
+        <v>0.6302009507147801</v>
       </c>
       <c r="F24" t="n">
-        <v>4.00185960735278</v>
+        <v>2.310736819287527</v>
       </c>
     </row>
     <row r="25">
@@ -921,19 +909,19 @@
         <v>2048</v>
       </c>
       <c r="B25" t="n">
-        <v>41.28524864111295</v>
+        <v>61.56388038246534</v>
       </c>
       <c r="C25" t="n">
         <v>113.6498546930506</v>
       </c>
       <c r="D25" t="n">
-        <v>72.36460605193761</v>
+        <v>52.08597431058522</v>
       </c>
       <c r="E25" t="n">
-        <v>1.047894502192761</v>
+        <v>0.5964681739063735</v>
       </c>
       <c r="F25" t="n">
-        <v>3.842279841373459</v>
+        <v>2.187049970990036</v>
       </c>
     </row>
     <row r="26">
@@ -941,19 +929,19 @@
         <v>2049</v>
       </c>
       <c r="B26" t="n">
-        <v>40.27901955874349</v>
+        <v>60.99929899233491</v>
       </c>
       <c r="C26" t="n">
         <v>113.6498545916505</v>
       </c>
       <c r="D26" t="n">
-        <v>73.37083503290704</v>
+        <v>52.65055559931562</v>
       </c>
       <c r="E26" t="n">
-        <v>1.006228980969425</v>
+        <v>0.5645812887303947</v>
       </c>
       <c r="F26" t="n">
-        <v>3.689506263554558</v>
+        <v>2.070131392011447</v>
       </c>
     </row>
     <row r="27">
@@ -961,19 +949,19 @@
         <v>2050</v>
       </c>
       <c r="B27" t="n">
-        <v>39.31268951070888</v>
+        <v>60.46486477990931</v>
       </c>
       <c r="C27" t="n">
         <v>113.6498544992957</v>
       </c>
       <c r="D27" t="n">
-        <v>74.33716498858685</v>
+        <v>53.18498971938642</v>
       </c>
       <c r="E27" t="n">
-        <v>0.9663299556798108</v>
+        <v>0.5344341200707987</v>
       </c>
       <c r="F27" t="n">
-        <v>3.54320983749264</v>
+        <v>1.959591773592929</v>
       </c>
     </row>
     <row r="28">
@@ -981,19 +969,19 @@
         <v>2051</v>
       </c>
       <c r="B28" t="n">
-        <v>38.38457592214925</v>
+        <v>59.95893708993925</v>
       </c>
       <c r="C28" t="n">
         <v>113.6498544151793</v>
       </c>
       <c r="D28" t="n">
-        <v>75.26527849303005</v>
+        <v>53.69091732524006</v>
       </c>
       <c r="E28" t="n">
-        <v>0.9281135044432034</v>
+        <v>0.5059276058536426</v>
       </c>
       <c r="F28" t="n">
-        <v>3.403082849625079</v>
+        <v>1.855067888130023</v>
       </c>
     </row>
     <row r="29">
@@ -1001,19 +989,19 @@
         <v>2052</v>
       </c>
       <c r="B29" t="n">
-        <v>37.49307511760814</v>
+        <v>59.47996801214418</v>
       </c>
       <c r="C29" t="n">
         <v>113.6498543385664</v>
       </c>
       <c r="D29" t="n">
-        <v>76.15677922095824</v>
+        <v>54.16988632642221</v>
       </c>
       <c r="E29" t="n">
-        <v>0.8915007279281895</v>
+        <v>0.4789690011821506</v>
       </c>
       <c r="F29" t="n">
-        <v>3.268836002403361</v>
+        <v>1.756219671001219</v>
       </c>
     </row>
     <row r="30">
@@ -1021,19 +1009,19 @@
         <v>2053</v>
       </c>
       <c r="B30" t="n">
-        <v>36.6366578394839</v>
+        <v>59.02649665134803</v>
       </c>
       <c r="C30" t="n">
         <v>113.6498542687876</v>
       </c>
       <c r="D30" t="n">
-        <v>77.01319642930366</v>
+        <v>54.62335761743953</v>
       </c>
       <c r="E30" t="n">
-        <v>0.8564172083454196</v>
+        <v>0.4534712910173226</v>
       </c>
       <c r="F30" t="n">
-        <v>3.140196430599872</v>
+        <v>1.662728067063516</v>
       </c>
     </row>
     <row r="31">
@@ -1041,19 +1029,19 @@
         <v>2054</v>
       </c>
       <c r="B31" t="n">
-        <v>35.81386516568909</v>
+        <v>58.5971438625217</v>
       </c>
       <c r="C31" t="n">
         <v>113.6498542052333</v>
       </c>
       <c r="D31" t="n">
-        <v>77.83598903954422</v>
+        <v>55.05271034271161</v>
       </c>
       <c r="E31" t="n">
-        <v>0.8227926102405547</v>
+        <v>0.4293527252720821</v>
       </c>
       <c r="F31" t="n">
-        <v>3.016906237548701</v>
+        <v>1.574293325997634</v>
       </c>
     </row>
     <row r="32">
@@ -1061,19 +1049,19 @@
         <v>2055</v>
       </c>
       <c r="B32" t="n">
-        <v>35.02330474346503</v>
+        <v>58.19060737482108</v>
       </c>
       <c r="C32" t="n">
         <v>113.6498541473483</v>
       </c>
       <c r="D32" t="n">
-        <v>78.6265494038833</v>
+        <v>55.45924677252726</v>
       </c>
       <c r="E32" t="n">
-        <v>0.7905603643390862</v>
+        <v>0.4065364298156453</v>
       </c>
       <c r="F32" t="n">
-        <v>2.898721335909983</v>
+        <v>1.490633575990699</v>
       </c>
     </row>
     <row r="33">
@@ -1081,19 +1069,19 @@
         <v>2056</v>
       </c>
       <c r="B33" t="n">
-        <v>34.26364728796553</v>
+        <v>57.80565725419996</v>
       </c>
       <c r="C33" t="n">
         <v>113.6498540946269</v>
       </c>
       <c r="D33" t="n">
-        <v>79.38620680666133</v>
+        <v>55.8441968404269</v>
       </c>
       <c r="E33" t="n">
-        <v>0.7596574027780321</v>
+        <v>0.3849500678996378</v>
       </c>
       <c r="F33" t="n">
-        <v>2.785410476852784</v>
+        <v>1.411483582298672</v>
       </c>
     </row>
     <row r="34">
@@ -1101,19 +1089,19 @@
         <v>2057</v>
       </c>
       <c r="B34" t="n">
-        <v>33.53362331154846</v>
+        <v>57.44113166848403</v>
       </c>
       <c r="C34" t="n">
         <v>113.6498540466084</v>
       </c>
       <c r="D34" t="n">
-        <v>80.11623073505993</v>
+        <v>56.20872237812436</v>
       </c>
       <c r="E34" t="n">
-        <v>0.7300239283985945</v>
+        <v>0.3645255376974603</v>
       </c>
       <c r="F34" t="n">
-        <v>2.67675440412818</v>
+        <v>1.336593638224021</v>
       </c>
     </row>
     <row r="35">
@@ -1121,19 +1109,19 @@
         <v>2058</v>
       </c>
       <c r="B35" t="n">
-        <v>32.83202005941531</v>
+        <v>57.09593292712008</v>
       </c>
       <c r="C35" t="n">
         <v>113.6498540028733</v>
       </c>
       <c r="D35" t="n">
-        <v>80.81783394345797</v>
+        <v>56.5539210757532</v>
       </c>
       <c r="E35" t="n">
-        <v>0.7016032083980406</v>
+        <v>0.3451986976288453</v>
       </c>
       <c r="F35" t="n">
-        <v>2.572545097459482</v>
+        <v>1.265728557972433</v>
       </c>
     </row>
     <row r="36">
@@ -1141,19 +1129,19 @@
         <v>2059</v>
       </c>
       <c r="B36" t="n">
-        <v>32.15767863287041</v>
+        <v>56.76902377291198</v>
       </c>
       <c r="C36" t="n">
         <v>113.6498539630395</v>
       </c>
       <c r="D36" t="n">
-        <v>81.49217533016909</v>
+        <v>56.88083019012753</v>
       </c>
       <c r="E36" t="n">
-        <v>0.6743413867111201</v>
+        <v>0.3269091143743239</v>
       </c>
       <c r="F36" t="n">
-        <v>2.47258508460744</v>
+        <v>1.198666752705854</v>
       </c>
     </row>
     <row r="37">
@@ -1161,19 +1149,19 @@
         <v>2060</v>
       </c>
       <c r="B37" t="n">
-        <v>31.50949128490851</v>
+        <v>56.45942390638449</v>
       </c>
       <c r="C37" t="n">
         <v>113.6498539267591</v>
       </c>
       <c r="D37" t="n">
-        <v>82.14036264185054</v>
+        <v>57.19043002037456</v>
       </c>
       <c r="E37" t="n">
-        <v>0.648187311681454</v>
+        <v>0.3095998302470306</v>
       </c>
       <c r="F37" t="n">
-        <v>2.376686809498665</v>
+        <v>1.135199377572446</v>
       </c>
     </row>
     <row r="38">
@@ -1181,19 +1169,19 @@
         <v>2061</v>
       </c>
       <c r="B38" t="n">
-        <v>30.88639887507928</v>
+        <v>56.16620672575284</v>
       </c>
       <c r="C38" t="n">
         <v>113.6498538937149</v>
       </c>
       <c r="D38" t="n">
-        <v>82.76345501863565</v>
+        <v>57.4836471679621</v>
       </c>
       <c r="E38" t="n">
-        <v>0.6230923767851095</v>
+        <v>0.2932171475875407</v>
       </c>
       <c r="F38" t="n">
-        <v>2.284672048212068</v>
+        <v>1.075129541154316</v>
       </c>
     </row>
     <row r="39">
@@ -1201,19 +1189,19 @@
         <v>2062</v>
       </c>
       <c r="B39" t="n">
-        <v>30.28738847214539</v>
+        <v>55.88849626723789</v>
       </c>
       <c r="C39" t="n">
         <v>113.6498538636185</v>
       </c>
       <c r="D39" t="n">
-        <v>83.36246539147317</v>
+        <v>57.76135759638066</v>
       </c>
       <c r="E39" t="n">
-        <v>0.5990103728375118</v>
+        <v>0.2777104284185583</v>
       </c>
       <c r="F39" t="n">
-        <v>2.196371367070876</v>
+        <v>1.018271570868047</v>
       </c>
     </row>
     <row r="40">
@@ -1221,19 +1209,19 @@
         <v>2063</v>
       </c>
       <c r="B40" t="n">
-        <v>29.71149109423422</v>
+        <v>55.62546433187906</v>
       </c>
       <c r="C40" t="n">
         <v>113.6498538362068</v>
       </c>
       <c r="D40" t="n">
-        <v>83.93836274197257</v>
+        <v>58.02438950432773</v>
       </c>
       <c r="E40" t="n">
-        <v>0.5758973504994032</v>
+        <v>0.2630319079470738</v>
       </c>
       <c r="F40" t="n">
-        <v>2.111623618497811</v>
+        <v>0.9644503291392704</v>
       </c>
     </row>
     <row r="41">
@@ -1241,19 +1229,19 @@
         <v>2064</v>
       </c>
       <c r="B41" t="n">
-        <v>29.15777957712991</v>
+        <v>55.37632778618033</v>
       </c>
       <c r="C41" t="n">
         <v>113.6498538112403</v>
       </c>
       <c r="D41" t="n">
-        <v>84.49207423411042</v>
+        <v>58.27352602505999</v>
       </c>
       <c r="E41" t="n">
-        <v>0.5537114921378503</v>
+        <v>0.2491365207322644</v>
       </c>
       <c r="F41" t="n">
-        <v>2.030275471172118</v>
+        <v>0.9135005760183029</v>
       </c>
     </row>
     <row r="42">
@@ -1261,19 +1249,19 @@
         <v>2065</v>
       </c>
       <c r="B42" t="n">
-        <v>28.62536656214836</v>
+        <v>55.14034602495217</v>
       </c>
       <c r="C42" t="n">
         <v>113.6498537885009</v>
       </c>
       <c r="D42" t="n">
-        <v>85.02448722635256</v>
+        <v>58.50950776354875</v>
       </c>
       <c r="E42" t="n">
-        <v>0.5324129922421434</v>
+        <v>0.2359817384887535</v>
       </c>
       <c r="F42" t="n">
-        <v>1.952180971554526</v>
+        <v>0.8652663744587628</v>
       </c>
     </row>
   </sheetData>
